--- a/ananthaDeath.xlsx
+++ b/ananthaDeath.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\nir\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0852866C-C19A-4729-9361-46F6A19619C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDC57F87-CE21-4D06-89C5-833C194DB090}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{9B90ECA5-DDCC-4CD7-B437-9892999844C0}"/>
   </bookViews>
@@ -96,7 +96,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="416" uniqueCount="278">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="413" uniqueCount="277">
   <si>
     <t>xerox</t>
   </si>
@@ -447,9 +447,6 @@
   </si>
   <si>
     <t>130050399595/1</t>
-  </si>
-  <si>
-    <t>FDR-online</t>
   </si>
   <si>
     <t>latha</t>
@@ -1313,7 +1310,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="74">
+  <cellXfs count="75">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1450,6 +1447,7 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="17" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="14" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -2046,7 +2044,7 @@
         <v>1047715.1</v>
       </c>
       <c r="N17" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="18" spans="1:18">
@@ -2075,10 +2073,10 @@
         <v>35000</v>
       </c>
       <c r="N18" t="s">
+        <v>117</v>
+      </c>
+      <c r="Q18" t="s">
         <v>118</v>
-      </c>
-      <c r="Q18" t="s">
-        <v>119</v>
       </c>
     </row>
     <row r="19" spans="1:18">
@@ -2331,7 +2329,7 @@
         <v>45698</v>
       </c>
       <c r="N26" s="9" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="O26" s="6">
         <v>-50011</v>
@@ -2369,7 +2367,7 @@
         <v>45699</v>
       </c>
       <c r="N27" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="O27" s="6">
         <v>40000</v>
@@ -2413,7 +2411,7 @@
         <v>45705</v>
       </c>
       <c r="N28" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="O28" s="6">
         <v>-49000</v>
@@ -2454,7 +2452,7 @@
         <v>45717</v>
       </c>
       <c r="N29" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="O29" s="6">
         <v>50000</v>
@@ -2486,13 +2484,13 @@
         <v>57</v>
       </c>
       <c r="N30" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="O30" s="6">
         <v>-2000</v>
       </c>
       <c r="Q30" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="31" spans="1:18">
@@ -2521,7 +2519,7 @@
         <v>57</v>
       </c>
       <c r="N31" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="O31" s="6">
         <v>45000</v>
@@ -2598,7 +2596,7 @@
         <v>57</v>
       </c>
       <c r="N33" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="O33" s="6">
         <v>-53000</v>
@@ -2710,7 +2708,7 @@
         <v>57</v>
       </c>
       <c r="N36" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="O36" s="6">
         <v>-50000</v>
@@ -2777,7 +2775,7 @@
         <v>15000</v>
       </c>
       <c r="N38" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="O38" s="6">
         <v>-1100</v>
@@ -2833,7 +2831,7 @@
         <v>6000</v>
       </c>
       <c r="N40" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="O40">
         <v>-54530</v>
@@ -2915,7 +2913,7 @@
       <c r="J43" s="11"/>
       <c r="K43" s="11"/>
       <c r="N43" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="O43">
         <v>-17260</v>
@@ -2954,10 +2952,10 @@
         <v>675.6</v>
       </c>
       <c r="Q44" t="s">
+        <v>178</v>
+      </c>
+      <c r="R44" t="s">
         <v>179</v>
-      </c>
-      <c r="R44" t="s">
-        <v>180</v>
       </c>
     </row>
     <row r="45" spans="2:18">
@@ -3040,7 +3038,7 @@
       <c r="J47" s="11"/>
       <c r="K47" s="11"/>
       <c r="Q47" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="R47">
         <v>40000</v>
@@ -3186,7 +3184,7 @@
     </row>
     <row r="54" spans="2:18">
       <c r="B54" s="9" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C54">
         <v>12080</v>
@@ -3283,7 +3281,7 @@
     </row>
     <row r="58" spans="2:18">
       <c r="B58" s="9" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C58">
         <v>12070</v>
@@ -3336,7 +3334,7 @@
     </row>
     <row r="60" spans="2:18">
       <c r="B60" s="9" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C60">
         <v>6500</v>
@@ -3432,7 +3430,7 @@
     </row>
     <row r="64" spans="2:18">
       <c r="B64" s="9" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C64">
         <v>6500</v>
@@ -3571,7 +3569,7 @@
     </row>
     <row r="69" spans="2:18">
       <c r="B69" s="9" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C69">
         <v>6250</v>
@@ -3787,13 +3785,13 @@
         <v>-1250</v>
       </c>
       <c r="K76" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="L76" t="s">
         <v>23</v>
       </c>
       <c r="M76" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="N76" s="9">
         <v>45689</v>
@@ -3821,7 +3819,7 @@
     </row>
     <row r="78" spans="2:18">
       <c r="G78" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="H78">
         <v>-325</v>
@@ -3839,7 +3837,7 @@
         <v>130000</v>
       </c>
       <c r="G79" s="16" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="H79">
         <v>15000</v>
@@ -3856,7 +3854,7 @@
         <v>45484</v>
       </c>
       <c r="G80" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="H80">
         <v>13500</v>
@@ -3891,7 +3889,7 @@
         <v>45535</v>
       </c>
       <c r="G81" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="H81">
         <v>7000</v>
@@ -3911,7 +3909,7 @@
         <v>45603</v>
       </c>
       <c r="G82" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="H82">
         <v>-600</v>
@@ -3937,7 +3935,7 @@
         <v>45692</v>
       </c>
       <c r="G83" s="16" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H83">
         <v>15000</v>
@@ -3963,7 +3961,7 @@
         <v>45716</v>
       </c>
       <c r="G84" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="H84">
         <v>13500</v>
@@ -3993,7 +3991,7 @@
         <v>45751</v>
       </c>
       <c r="G85" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="H85">
         <v>7000</v>
@@ -4019,7 +4017,7 @@
         <v>45778</v>
       </c>
       <c r="G86" s="16" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="H86">
         <v>15000</v>
@@ -4045,7 +4043,7 @@
         <v>45832</v>
       </c>
       <c r="G87" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="H87">
         <v>13500</v>
@@ -4071,7 +4069,7 @@
         <v>45871</v>
       </c>
       <c r="G88" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="H88">
         <v>7000</v>
@@ -4091,7 +4089,7 @@
     </row>
     <row r="89" spans="3:14">
       <c r="G89" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H89">
         <v>15000</v>
@@ -4111,7 +4109,7 @@
     </row>
     <row r="90" spans="3:14">
       <c r="G90" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H90">
         <v>13500</v>
@@ -4131,7 +4129,7 @@
     </row>
     <row r="91" spans="3:14">
       <c r="G91" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H91">
         <v>7350</v>
@@ -4151,7 +4149,7 @@
     </row>
     <row r="92" spans="3:14">
       <c r="G92" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="H92">
         <v>-11018</v>
@@ -4171,7 +4169,7 @@
     </row>
     <row r="93" spans="3:14">
       <c r="G93" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="H93">
         <v>13500</v>
@@ -4191,7 +4189,7 @@
     </row>
     <row r="94" spans="3:14">
       <c r="G94" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="H94">
         <v>15000</v>
@@ -4211,7 +4209,7 @@
     </row>
     <row r="95" spans="3:14">
       <c r="G95" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="H95">
         <v>7350</v>
@@ -4231,7 +4229,7 @@
     </row>
     <row r="96" spans="3:14">
       <c r="G96" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="H96">
         <v>13500</v>
@@ -4251,7 +4249,7 @@
     </row>
     <row r="97" spans="1:13">
       <c r="G97" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="H97">
         <v>15000</v>
@@ -4271,7 +4269,7 @@
     </row>
     <row r="98" spans="1:13">
       <c r="G98" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="H98">
         <v>7350</v>
@@ -4291,7 +4289,7 @@
     </row>
     <row r="99" spans="1:13">
       <c r="G99" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="H99">
         <v>13500</v>
@@ -4311,7 +4309,7 @@
     </row>
     <row r="100" spans="1:13">
       <c r="G100" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H100">
         <v>15000</v>
@@ -4331,7 +4329,7 @@
     </row>
     <row r="101" spans="1:13">
       <c r="G101" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="H101">
         <v>7000</v>
@@ -4351,7 +4349,7 @@
     </row>
     <row r="102" spans="1:13">
       <c r="G102" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="H102">
         <v>13500</v>
@@ -4375,7 +4373,7 @@
         <v>565600</v>
       </c>
       <c r="G103" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H103">
         <v>15000</v>
@@ -4395,10 +4393,10 @@
     </row>
     <row r="104" spans="1:13">
       <c r="B104" s="9" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="G104" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="H104">
         <v>7700</v>
@@ -4444,7 +4442,7 @@
         <v>45444</v>
       </c>
       <c r="D106" s="4" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="E106">
         <f>12000*8</f>
@@ -4506,13 +4504,13 @@
         <v>45536</v>
       </c>
       <c r="D108" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="E108">
         <v>20000</v>
       </c>
       <c r="G108" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="H108">
         <v>7350</v>
@@ -4538,13 +4536,13 @@
         <v>45566</v>
       </c>
       <c r="D109" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="E109">
         <v>-120000</v>
       </c>
       <c r="G109" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="H109">
         <v>15000</v>
@@ -4574,7 +4572,7 @@
         <v>34000</v>
       </c>
       <c r="G110" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="H110">
         <v>13500</v>
@@ -4614,7 +4612,7 @@
         <v>45658</v>
       </c>
       <c r="G112" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="H112">
         <v>15000</v>
@@ -4628,7 +4626,7 @@
         <v>45689</v>
       </c>
       <c r="G113" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="H113">
         <v>13500</v>
@@ -4698,7 +4696,7 @@
         <v>45839</v>
       </c>
       <c r="G118" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="H118">
         <v>15000</v>
@@ -4712,7 +4710,7 @@
         <v>45870</v>
       </c>
       <c r="G119" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="H119">
         <v>13500</v>
@@ -4720,14 +4718,14 @@
     </row>
     <row r="120" spans="1:8">
       <c r="B120" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C120">
         <f>14*12000</f>
         <v>168000</v>
       </c>
       <c r="G120" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="H120">
         <v>7350</v>
@@ -4735,13 +4733,13 @@
     </row>
     <row r="121" spans="1:8">
       <c r="B121" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C121">
         <v>-130000</v>
       </c>
       <c r="G121" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="H121">
         <v>15000</v>
@@ -4749,14 +4747,14 @@
     </row>
     <row r="122" spans="1:8">
       <c r="B122" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C122">
         <f>SUBTOTAL(9,C120:C121)</f>
         <v>38000</v>
       </c>
       <c r="G122" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="H122">
         <v>13500</v>
@@ -4764,7 +4762,7 @@
     </row>
     <row r="123" spans="1:8">
       <c r="G123" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="H123">
         <v>7350</v>
@@ -4772,7 +4770,7 @@
     </row>
     <row r="124" spans="1:8">
       <c r="G124" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="H124">
         <v>15000</v>
@@ -4780,7 +4778,7 @@
     </row>
     <row r="125" spans="1:8">
       <c r="G125" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H125">
         <v>13500</v>
@@ -4788,7 +4786,7 @@
     </row>
     <row r="126" spans="1:8">
       <c r="G126" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="H126">
         <v>7350</v>
@@ -4796,7 +4794,7 @@
     </row>
     <row r="127" spans="1:8">
       <c r="G127" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H127">
         <v>15000</v>
@@ -4804,7 +4802,7 @@
     </row>
     <row r="128" spans="1:8">
       <c r="G128" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H128">
         <v>13500</v>
@@ -4812,7 +4810,7 @@
     </row>
     <row r="129" spans="7:8">
       <c r="G129" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H129">
         <v>7350</v>
@@ -4820,7 +4818,7 @@
     </row>
     <row r="130" spans="7:8">
       <c r="G130" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="H130">
         <v>-1502</v>
@@ -4836,7 +4834,7 @@
     </row>
     <row r="132" spans="7:8">
       <c r="G132" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="H132">
         <v>-11018</v>
@@ -4844,7 +4842,7 @@
     </row>
     <row r="133" spans="7:8">
       <c r="G133" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="H133" s="15">
         <v>15750</v>
@@ -4852,7 +4850,7 @@
     </row>
     <row r="134" spans="7:8">
       <c r="G134" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="H134" s="15">
         <v>13500</v>
@@ -4860,7 +4858,7 @@
     </row>
     <row r="135" spans="7:8">
       <c r="G135" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="H135" s="15">
         <v>7350</v>
@@ -4868,7 +4866,7 @@
     </row>
     <row r="136" spans="7:8">
       <c r="G136" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="H136" s="15">
         <v>15750</v>
@@ -4876,7 +4874,7 @@
     </row>
     <row r="137" spans="7:8">
       <c r="G137" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="H137" s="15">
         <v>13500</v>
@@ -4884,7 +4882,7 @@
     </row>
     <row r="138" spans="7:8">
       <c r="G138" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H138" s="15">
         <v>7350</v>
@@ -4892,7 +4890,7 @@
     </row>
     <row r="139" spans="7:8">
       <c r="G139" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H139" s="15">
         <v>15750</v>
@@ -4900,7 +4898,7 @@
     </row>
     <row r="140" spans="7:8">
       <c r="G140" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="H140" s="15">
         <v>13500</v>
@@ -4908,7 +4906,7 @@
     </row>
     <row r="141" spans="7:8">
       <c r="G141" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="H141" s="15">
         <v>7350</v>
@@ -4916,7 +4914,7 @@
     </row>
     <row r="142" spans="7:8">
       <c r="G142" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="H142" s="15">
         <v>15750</v>
@@ -4924,7 +4922,7 @@
     </row>
     <row r="143" spans="7:8">
       <c r="G143" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H143" s="15">
         <v>13500</v>
@@ -4932,7 +4930,7 @@
     </row>
     <row r="144" spans="7:8">
       <c r="G144" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="H144" s="15">
         <v>7350</v>
@@ -4940,7 +4938,7 @@
     </row>
     <row r="145" spans="7:8">
       <c r="G145" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="H145" s="15">
         <v>15750</v>
@@ -4948,7 +4946,7 @@
     </row>
     <row r="146" spans="7:8">
       <c r="G146" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="H146" s="15">
         <v>13500</v>
@@ -4956,7 +4954,7 @@
     </row>
     <row r="147" spans="7:8">
       <c r="G147" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="H147" s="15">
         <v>7350</v>
@@ -4964,7 +4962,7 @@
     </row>
     <row r="148" spans="7:8">
       <c r="G148" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="H148" s="15">
         <v>15750</v>
@@ -4972,7 +4970,7 @@
     </row>
     <row r="149" spans="7:8">
       <c r="G149" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="H149" s="15">
         <v>13500</v>
@@ -4980,7 +4978,7 @@
     </row>
     <row r="150" spans="7:8">
       <c r="G150" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H150" s="15">
         <v>7350</v>
@@ -4988,7 +4986,7 @@
     </row>
     <row r="151" spans="7:8">
       <c r="G151" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="H151" s="15">
         <v>15750</v>
@@ -4996,7 +4994,7 @@
     </row>
     <row r="152" spans="7:8">
       <c r="G152" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H152" s="15">
         <v>13500</v>
@@ -5004,7 +5002,7 @@
     </row>
     <row r="153" spans="7:8">
       <c r="G153" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="H153" s="15">
         <v>7350</v>
@@ -5012,7 +5010,7 @@
     </row>
     <row r="154" spans="7:8">
       <c r="G154" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="H154" s="15">
         <v>15750</v>
@@ -5020,7 +5018,7 @@
     </row>
     <row r="155" spans="7:8">
       <c r="G155" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H155" s="15">
         <v>13500</v>
@@ -5028,7 +5026,7 @@
     </row>
     <row r="156" spans="7:8">
       <c r="G156" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="H156" s="15">
         <v>7350</v>
@@ -5036,17 +5034,17 @@
     </row>
     <row r="157" spans="7:8">
       <c r="G157" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="158" spans="7:8">
       <c r="G158" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="159" spans="7:8">
       <c r="G159" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
   </sheetData>
@@ -5058,7 +5056,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C44A5A3D-78C1-4CED-B2CA-FA2A508121D8}">
-  <dimension ref="A1:AP115"/>
+  <dimension ref="A1:AP132"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="19.109375" customWidth="1"/>
@@ -5107,10 +5105,10 @@
       </c>
       <c r="F2" s="11"/>
       <c r="AH2" t="s">
+        <v>140</v>
+      </c>
+      <c r="AI2" t="s">
         <v>141</v>
-      </c>
-      <c r="AI2" t="s">
-        <v>142</v>
       </c>
       <c r="AL2">
         <v>30000</v>
@@ -5134,7 +5132,7 @@
       </c>
       <c r="F3" s="11"/>
       <c r="AH3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="AI3">
         <v>30000</v>
@@ -5168,7 +5166,7 @@
       </c>
       <c r="F4" s="11"/>
       <c r="AH4" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="AI4">
         <v>-5000</v>
@@ -5236,7 +5234,7 @@
         <v>46082</v>
       </c>
       <c r="AH6" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="AI6">
         <v>-5000</v>
@@ -5432,16 +5430,16 @@
         <v>927</v>
       </c>
       <c r="R15" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="AH15" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="AI15">
         <v>-530</v>
       </c>
       <c r="AK15" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="AL15" s="15">
         <v>-5000</v>
@@ -5478,14 +5476,14 @@
       <c r="Z16" s="9"/>
       <c r="AA16" s="9"/>
       <c r="AH16" s="9" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="AI16">
         <v>-45</v>
       </c>
       <c r="AJ16" s="9"/>
       <c r="AK16" s="9" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="AL16" s="15">
         <v>-1500</v>
@@ -5516,13 +5514,13 @@
         <v>1888</v>
       </c>
       <c r="AH17" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="AI17">
         <v>-390</v>
       </c>
       <c r="AK17" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="AL17" s="15">
         <v>-1500</v>
@@ -5530,7 +5528,7 @@
     </row>
     <row r="18" spans="1:42" ht="28.8">
       <c r="A18" s="67" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B18" s="18">
         <v>45771</v>
@@ -5552,10 +5550,10 @@
         <v>22550</v>
       </c>
       <c r="R18" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="AH18" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="AI18">
         <v>-170</v>
@@ -5565,7 +5563,7 @@
         <v>65800</v>
       </c>
       <c r="AN18" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="AO18">
         <v>200</v>
@@ -5595,7 +5593,7 @@
         <v>2130</v>
       </c>
       <c r="AH19" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="AI19">
         <v>-20</v>
@@ -5604,7 +5602,7 @@
         <v>-30700</v>
       </c>
       <c r="AN19" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="AO19">
         <v>200</v>
@@ -5619,14 +5617,14 @@
         <v>-40</v>
       </c>
       <c r="AK20" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="AL20">
         <f>SUM(AL18:AL19)</f>
         <v>35100</v>
       </c>
       <c r="AN20" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="AP20">
         <v>100</v>
@@ -5634,7 +5632,7 @@
     </row>
     <row r="21" spans="1:42">
       <c r="AH21" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="AI21">
         <v>-145</v>
@@ -5650,13 +5648,13 @@
       <c r="E22" s="11"/>
       <c r="F22" s="11"/>
       <c r="AH22" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="AI22">
         <v>-54</v>
       </c>
       <c r="AJ22" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="23" spans="1:42">
@@ -5675,7 +5673,7 @@
       <c r="E23" s="20"/>
       <c r="F23" s="11"/>
       <c r="AH23" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="AI23">
         <v>-690</v>
@@ -5699,7 +5697,7 @@
       </c>
       <c r="F24" s="11"/>
       <c r="AH24" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="AI24">
         <v>-400</v>
@@ -5732,7 +5730,7 @@
         <v>337</v>
       </c>
       <c r="AH25" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="AI25">
         <v>-50</v>
@@ -5801,7 +5799,7 @@
         <v>337</v>
       </c>
       <c r="AH27" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="AI27">
         <v>-95</v>
@@ -5831,7 +5829,7 @@
         <v>337</v>
       </c>
       <c r="AH28" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="AI28">
         <v>-33</v>
@@ -5855,7 +5853,7 @@
       </c>
       <c r="F29" s="11"/>
       <c r="AH29" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="AI29">
         <v>-14000</v>
@@ -5882,7 +5880,7 @@
       </c>
       <c r="F30" s="11"/>
       <c r="AH30" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="AI30">
         <v>-168</v>
@@ -5909,7 +5907,7 @@
       </c>
       <c r="F31" s="11"/>
       <c r="AH31" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="AI31">
         <v>-13</v>
@@ -5937,7 +5935,7 @@
       </c>
       <c r="F32" s="11"/>
       <c r="AH32" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="AI32">
         <v>-10</v>
@@ -5980,7 +5978,7 @@
       <c r="E34" s="20"/>
       <c r="F34" s="11"/>
       <c r="AH34" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="AI34" s="15">
         <v>-5000</v>
@@ -6006,7 +6004,7 @@
       <c r="E35" s="20"/>
       <c r="F35" s="11"/>
       <c r="AH35" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="AI35" s="15">
         <v>-1500</v>
@@ -6022,17 +6020,17 @@
       <c r="C36" s="18">
         <v>46176</v>
       </c>
-      <c r="D36" s="11">
+      <c r="D36" s="69">
         <v>49000</v>
       </c>
       <c r="E36" s="22">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="F36" s="11">
         <v>367</v>
       </c>
       <c r="AH36" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="AI36" s="15">
         <v>-1500</v>
@@ -6048,11 +6046,11 @@
       <c r="C37" s="18">
         <v>46180</v>
       </c>
-      <c r="D37" s="11">
+      <c r="D37" s="69">
         <v>60000</v>
       </c>
       <c r="E37" s="22">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="F37" s="11">
         <v>450</v>
@@ -6150,7 +6148,7 @@
     </row>
     <row r="44" spans="1:40">
       <c r="A44" s="62" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B44" s="18">
         <v>46159</v>
@@ -6168,7 +6166,7 @@
     </row>
     <row r="45" spans="1:40">
       <c r="A45" s="62" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B45" s="18">
         <v>46093</v>
@@ -6194,7 +6192,7 @@
       <c r="C46" s="18">
         <v>46214</v>
       </c>
-      <c r="D46" s="11">
+      <c r="D46" s="69">
         <v>49000</v>
       </c>
       <c r="E46" s="20">
@@ -6212,7 +6210,7 @@
       <c r="C47" s="18">
         <v>46214</v>
       </c>
-      <c r="D47" s="11">
+      <c r="D47" s="69">
         <v>49000</v>
       </c>
       <c r="E47" s="20">
@@ -6402,7 +6400,7 @@
     </row>
     <row r="58" spans="1:10">
       <c r="A58" s="62" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B58" s="18">
         <v>45793</v>
@@ -6419,7 +6417,7 @@
     </row>
     <row r="59" spans="1:10">
       <c r="A59" s="62" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B59" s="18">
         <v>45916</v>
@@ -6436,7 +6434,7 @@
     </row>
     <row r="60" spans="1:10">
       <c r="A60" s="62" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B60" s="18">
         <v>45944</v>
@@ -6454,7 +6452,7 @@
     </row>
     <row r="61" spans="1:10">
       <c r="A61" s="62" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B61" s="18">
         <v>45945</v>
@@ -6581,7 +6579,7 @@
         <v>1953</v>
       </c>
       <c r="S68" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="69" spans="1:24">
@@ -6649,12 +6647,8 @@
       <c r="B73" s="18"/>
       <c r="C73" s="66"/>
       <c r="D73" s="11"/>
-      <c r="E73" s="20">
-        <v>7.7499999999999999E-2</v>
-      </c>
-      <c r="F73" s="11" t="s">
-        <v>117</v>
-      </c>
+      <c r="E73" s="20"/>
+      <c r="F73" s="11"/>
       <c r="J73">
         <v>2865</v>
       </c>
@@ -6667,19 +6661,13 @@
     </row>
     <row r="74" spans="1:24">
       <c r="A74" s="11" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B74" s="18"/>
       <c r="C74" s="63"/>
-      <c r="D74" s="11">
-        <v>70000</v>
-      </c>
-      <c r="E74" s="20">
-        <v>7.7499999999999999E-2</v>
-      </c>
-      <c r="F74" s="11" t="s">
-        <v>117</v>
-      </c>
+      <c r="D74" s="11"/>
+      <c r="E74" s="20"/>
+      <c r="F74" s="11"/>
       <c r="H74" s="1"/>
       <c r="K74">
         <v>1323</v>
@@ -6693,19 +6681,13 @@
     </row>
     <row r="75" spans="1:24">
       <c r="A75" s="11" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B75" s="18"/>
       <c r="C75" s="63"/>
-      <c r="D75" s="11">
-        <v>50000</v>
-      </c>
-      <c r="E75" s="20">
-        <v>7.7499999999999999E-2</v>
-      </c>
-      <c r="F75" s="11" t="s">
-        <v>117</v>
-      </c>
+      <c r="D75" s="11"/>
+      <c r="E75" s="20"/>
+      <c r="F75" s="11"/>
       <c r="K75">
         <v>955</v>
       </c>
@@ -6718,23 +6700,13 @@
     </row>
     <row r="76" spans="1:24">
       <c r="A76" s="11" t="s">
-        <v>135</v>
-      </c>
-      <c r="B76" s="18">
-        <v>45729</v>
-      </c>
-      <c r="C76" s="63">
-        <v>46173</v>
-      </c>
-      <c r="D76" s="11">
-        <v>52000</v>
-      </c>
-      <c r="E76" s="20">
-        <v>7.7499999999999999E-2</v>
-      </c>
-      <c r="F76" s="11" t="s">
-        <v>117</v>
-      </c>
+        <v>134</v>
+      </c>
+      <c r="B76" s="18"/>
+      <c r="C76" s="63"/>
+      <c r="D76" s="11"/>
+      <c r="E76" s="20"/>
+      <c r="F76" s="11"/>
       <c r="H76" s="1"/>
       <c r="L76">
         <v>1016</v>
@@ -6743,12 +6715,12 @@
         <v>1016</v>
       </c>
       <c r="R76" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="77" spans="1:24">
       <c r="A77" s="11" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B77" s="18">
         <v>45769</v>
@@ -6775,7 +6747,7 @@
     </row>
     <row r="78" spans="1:24">
       <c r="A78" s="11" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B78" s="18">
         <v>45792</v>
@@ -6802,7 +6774,7 @@
     </row>
     <row r="79" spans="1:24">
       <c r="A79" s="11" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B79" s="18">
         <v>45794</v>
@@ -6817,10 +6789,10 @@
         <v>7.7499999999999999E-2</v>
       </c>
       <c r="F79" s="11" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="H79" s="15" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="K79">
         <v>4884</v>
@@ -6834,7 +6806,7 @@
     </row>
     <row r="80" spans="1:24">
       <c r="A80" s="11" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B80" s="18">
         <v>45849</v>
@@ -6849,18 +6821,18 @@
         <v>7.0999999999999994E-2</v>
       </c>
       <c r="F80" s="11" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="H80" s="15" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P80">
         <v>984</v>
       </c>
     </row>
-    <row r="81" spans="1:17">
+    <row r="81" spans="1:20">
       <c r="A81" s="11" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B81" s="18">
         <v>45880</v>
@@ -6875,23 +6847,23 @@
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="F81" s="11" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="H81" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="Q81">
         <v>1182</v>
       </c>
     </row>
-    <row r="83" spans="1:17">
+    <row r="83" spans="1:20">
       <c r="A83" s="62" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B83" s="11"/>
       <c r="C83" s="11"/>
     </row>
-    <row r="84" spans="1:17">
+    <row r="84" spans="1:20">
       <c r="A84" s="11">
         <v>20182378659</v>
       </c>
@@ -6919,10 +6891,16 @@
         <f>L84/12</f>
         <v>20499.999999999996</v>
       </c>
-    </row>
-    <row r="85" spans="1:17">
+      <c r="T84">
+        <v>132000</v>
+      </c>
+    </row>
+    <row r="85" spans="1:20">
       <c r="A85" t="s">
-        <v>236</v>
+        <v>235</v>
+      </c>
+      <c r="B85">
+        <v>20195366872</v>
       </c>
       <c r="D85">
         <v>400000</v>
@@ -6932,12 +6910,17 @@
       <c r="M85">
         <v>36000</v>
       </c>
-    </row>
-    <row r="86" spans="1:17">
+      <c r="T85">
+        <v>52000</v>
+      </c>
+    </row>
+    <row r="86" spans="1:20">
       <c r="A86" s="11" t="s">
-        <v>236</v>
-      </c>
-      <c r="B86" s="11"/>
+        <v>235</v>
+      </c>
+      <c r="B86" s="11">
+        <v>20198288268</v>
+      </c>
       <c r="C86" s="11"/>
       <c r="D86" s="11">
         <v>400000</v>
@@ -6947,12 +6930,17 @@
       <c r="M86">
         <v>6000</v>
       </c>
-    </row>
-    <row r="87" spans="1:17">
+      <c r="T86">
+        <v>11000</v>
+      </c>
+    </row>
+    <row r="87" spans="1:20">
       <c r="A87" s="11" t="s">
-        <v>236</v>
-      </c>
-      <c r="B87" s="11"/>
+        <v>235</v>
+      </c>
+      <c r="B87" s="11">
+        <v>20216020979</v>
+      </c>
       <c r="C87" s="11"/>
       <c r="D87" s="11">
         <v>300000</v>
@@ -6963,18 +6951,24 @@
         <v>16000</v>
       </c>
     </row>
-    <row r="88" spans="1:17">
-      <c r="A88" s="11"/>
-      <c r="B88" s="11"/>
+    <row r="88" spans="1:20">
+      <c r="A88" s="11" t="s">
+        <v>235</v>
+      </c>
+      <c r="B88">
+        <v>20222932450</v>
+      </c>
       <c r="C88" s="11"/>
-      <c r="D88" s="11"/>
+      <c r="D88" s="11">
+        <v>250000</v>
+      </c>
       <c r="E88" s="11"/>
       <c r="F88" s="11"/>
       <c r="M88">
         <v>5550</v>
       </c>
     </row>
-    <row r="89" spans="1:17">
+    <row r="89" spans="1:20">
       <c r="M89">
         <f>SUM(M84:M88)</f>
         <v>84050</v>
@@ -6984,7 +6978,7 @@
         <v>1008600</v>
       </c>
     </row>
-    <row r="90" spans="1:17">
+    <row r="90" spans="1:20">
       <c r="E90">
         <f>(D84*0.074)/12</f>
         <v>5550</v>
@@ -6994,18 +6988,29 @@
         <v>16650</v>
       </c>
     </row>
-    <row r="91" spans="1:17">
+    <row r="91" spans="1:20">
       <c r="B91" s="5"/>
     </row>
-    <row r="93" spans="1:17">
+    <row r="93" spans="1:20">
       <c r="D93">
         <f>SUM(D2:D92)</f>
-        <v>8082000</v>
-      </c>
-    </row>
-    <row r="97" spans="1:18">
-      <c r="A97" s="71">
-        <v>46388</v>
+        <v>8160000</v>
+      </c>
+    </row>
+    <row r="96" spans="1:20">
+      <c r="B96" s="5">
+        <v>1350000</v>
+      </c>
+      <c r="C96" s="5">
+        <v>900000</v>
+      </c>
+      <c r="D96" s="5">
+        <v>3000000</v>
+      </c>
+    </row>
+    <row r="97" spans="1:20">
+      <c r="A97" s="72">
+        <v>46410</v>
       </c>
       <c r="B97">
         <v>30854</v>
@@ -7016,8 +7021,8 @@
       <c r="D97">
         <v>61500</v>
       </c>
-      <c r="E97" s="71">
-        <v>46753</v>
+      <c r="E97" s="72">
+        <v>46775</v>
       </c>
       <c r="F97">
         <v>30854</v>
@@ -7058,10 +7063,14 @@
       <c r="R97">
         <v>30854</v>
       </c>
-    </row>
-    <row r="98" spans="1:18">
-      <c r="A98" s="71">
-        <v>46419</v>
+      <c r="T97" s="5">
+        <f>SUM(B97:D97)</f>
+        <v>97854</v>
+      </c>
+    </row>
+    <row r="98" spans="1:20">
+      <c r="A98" s="72">
+        <v>46423</v>
       </c>
       <c r="B98">
         <v>30854</v>
@@ -7069,8 +7078,8 @@
       <c r="C98">
         <v>5500</v>
       </c>
-      <c r="E98" s="71">
-        <v>46784</v>
+      <c r="E98" s="72">
+        <v>46788</v>
       </c>
       <c r="F98">
         <v>30854</v>
@@ -7102,9 +7111,13 @@
       <c r="R98">
         <v>30854</v>
       </c>
-    </row>
-    <row r="99" spans="1:18">
-      <c r="A99" s="71">
+      <c r="T98" s="5">
+        <f>SUM(B98:D98)</f>
+        <v>36354</v>
+      </c>
+    </row>
+    <row r="99" spans="1:20">
+      <c r="A99" s="72">
         <v>46447</v>
       </c>
       <c r="B99">
@@ -7113,7 +7126,7 @@
       <c r="C99">
         <v>5500</v>
       </c>
-      <c r="E99" s="71">
+      <c r="E99" s="72">
         <v>46813</v>
       </c>
       <c r="F99">
@@ -7146,10 +7159,14 @@
       <c r="R99">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="1:18">
-      <c r="A100" s="71">
-        <v>46478</v>
+      <c r="T99" s="5">
+        <f t="shared" ref="T99:T108" si="0">SUM(B99:D99)</f>
+        <v>5500</v>
+      </c>
+    </row>
+    <row r="100" spans="1:20">
+      <c r="A100" s="72">
+        <v>46123</v>
       </c>
       <c r="B100">
         <v>23140</v>
@@ -7160,8 +7177,8 @@
       <c r="D100">
         <v>61500</v>
       </c>
-      <c r="E100" s="71">
-        <v>46844</v>
+      <c r="E100" s="72">
+        <v>46854</v>
       </c>
       <c r="F100">
         <v>23140</v>
@@ -7202,15 +7219,22 @@
       <c r="R100">
         <v>23140</v>
       </c>
-    </row>
-    <row r="101" spans="1:18">
-      <c r="A101" s="71">
+      <c r="T100" s="5">
+        <f t="shared" si="0"/>
+        <v>90140</v>
+      </c>
+    </row>
+    <row r="101" spans="1:20">
+      <c r="A101" s="72">
         <v>46508</v>
+      </c>
+      <c r="B101">
+        <v>0</v>
       </c>
       <c r="C101">
         <v>5500</v>
       </c>
-      <c r="E101" s="71">
+      <c r="E101" s="72">
         <v>46874</v>
       </c>
       <c r="G101">
@@ -7231,16 +7255,26 @@
       <c r="Q101" s="71">
         <v>47969</v>
       </c>
-    </row>
-    <row r="102" spans="1:18">
-      <c r="A102" s="71">
-        <v>46539</v>
+      <c r="T101" s="5">
+        <f t="shared" si="0"/>
+        <v>5500</v>
+      </c>
+    </row>
+    <row r="102" spans="1:20">
+      <c r="A102" s="72">
+        <v>46540</v>
+      </c>
+      <c r="B102">
+        <v>19284</v>
       </c>
       <c r="C102">
         <v>5500</v>
       </c>
-      <c r="E102" s="71">
-        <v>46905</v>
+      <c r="E102" s="72">
+        <v>46906</v>
+      </c>
+      <c r="F102">
+        <v>19284</v>
       </c>
       <c r="G102">
         <v>5500</v>
@@ -7248,22 +7282,38 @@
       <c r="I102" s="71">
         <v>47270</v>
       </c>
+      <c r="J102">
+        <v>19284</v>
+      </c>
       <c r="K102">
         <v>5500</v>
       </c>
       <c r="M102" s="71">
         <v>47635</v>
       </c>
+      <c r="N102">
+        <v>19284</v>
+      </c>
       <c r="O102">
         <v>5500</v>
       </c>
       <c r="Q102" s="71">
         <v>48000</v>
       </c>
-    </row>
-    <row r="103" spans="1:18">
-      <c r="A103" s="71">
+      <c r="R102">
+        <v>19284</v>
+      </c>
+      <c r="T102" s="5">
+        <f t="shared" si="0"/>
+        <v>24784</v>
+      </c>
+    </row>
+    <row r="103" spans="1:20">
+      <c r="A103" s="72">
         <v>46569</v>
+      </c>
+      <c r="B103" s="15">
+        <v>7713.5</v>
       </c>
       <c r="C103">
         <v>5500</v>
@@ -7271,7 +7321,7 @@
       <c r="D103">
         <v>61500</v>
       </c>
-      <c r="E103" s="71">
+      <c r="E103" s="72">
         <v>46935</v>
       </c>
       <c r="G103">
@@ -7301,15 +7351,22 @@
       <c r="Q103" s="71">
         <v>48030</v>
       </c>
-    </row>
-    <row r="104" spans="1:18">
-      <c r="A104" s="71">
+      <c r="T103" s="5">
+        <f t="shared" si="0"/>
+        <v>74713.5</v>
+      </c>
+    </row>
+    <row r="104" spans="1:20">
+      <c r="A104" s="72">
         <v>46600</v>
+      </c>
+      <c r="B104" s="15">
+        <v>19284</v>
       </c>
       <c r="C104">
         <v>5500</v>
       </c>
-      <c r="E104" s="71">
+      <c r="E104" s="72">
         <v>46966</v>
       </c>
       <c r="G104">
@@ -7330,15 +7387,22 @@
       <c r="Q104" s="71">
         <v>48061</v>
       </c>
-    </row>
-    <row r="105" spans="1:18">
-      <c r="A105" s="71">
+      <c r="T104" s="5">
+        <f t="shared" si="0"/>
+        <v>24784</v>
+      </c>
+    </row>
+    <row r="105" spans="1:20">
+      <c r="A105" s="72">
         <v>46631</v>
+      </c>
+      <c r="B105" s="15">
+        <v>3850</v>
       </c>
       <c r="C105">
         <v>5500</v>
       </c>
-      <c r="E105" s="71">
+      <c r="E105" s="72">
         <v>46997</v>
       </c>
       <c r="G105">
@@ -7359,10 +7423,17 @@
       <c r="Q105" s="71">
         <v>48092</v>
       </c>
-    </row>
-    <row r="106" spans="1:18">
-      <c r="A106" s="71">
+      <c r="T105" s="5">
+        <f t="shared" si="0"/>
+        <v>9350</v>
+      </c>
+    </row>
+    <row r="106" spans="1:20">
+      <c r="A106" s="72">
         <v>46661</v>
+      </c>
+      <c r="B106" s="15">
+        <v>13499</v>
       </c>
       <c r="C106">
         <v>5500</v>
@@ -7370,7 +7441,7 @@
       <c r="D106">
         <v>61500</v>
       </c>
-      <c r="E106" s="71">
+      <c r="E106" s="72">
         <v>47027</v>
       </c>
       <c r="G106">
@@ -7400,15 +7471,19 @@
       <c r="Q106" s="71">
         <v>48122</v>
       </c>
-    </row>
-    <row r="107" spans="1:18">
-      <c r="A107" s="71">
+      <c r="T106" s="5">
+        <f t="shared" si="0"/>
+        <v>80499</v>
+      </c>
+    </row>
+    <row r="107" spans="1:20">
+      <c r="A107" s="72">
         <v>46692</v>
       </c>
       <c r="C107">
         <v>5500</v>
       </c>
-      <c r="E107" s="71">
+      <c r="E107" s="72">
         <v>47058</v>
       </c>
       <c r="G107">
@@ -7429,15 +7504,19 @@
       <c r="Q107" s="71">
         <v>48153</v>
       </c>
-    </row>
-    <row r="108" spans="1:18">
-      <c r="A108" s="71">
+      <c r="T107" s="5">
+        <f t="shared" si="0"/>
+        <v>5500</v>
+      </c>
+    </row>
+    <row r="108" spans="1:20">
+      <c r="A108" s="72">
         <v>46722</v>
       </c>
       <c r="C108">
         <v>5500</v>
       </c>
-      <c r="E108" s="71">
+      <c r="E108" s="72">
         <v>47088</v>
       </c>
       <c r="G108">
@@ -7458,8 +7537,18 @@
       <c r="Q108" s="71">
         <v>48183</v>
       </c>
-    </row>
-    <row r="111" spans="1:18">
+      <c r="T108" s="5">
+        <f t="shared" si="0"/>
+        <v>5500</v>
+      </c>
+    </row>
+    <row r="110" spans="1:20">
+      <c r="T110" s="5">
+        <f>SUM(T97:T109)</f>
+        <v>460478.5</v>
+      </c>
+    </row>
+    <row r="111" spans="1:20">
       <c r="B111">
         <v>20500</v>
       </c>
@@ -7475,31 +7564,140 @@
         <f>D111/12</f>
         <v>1928.375</v>
       </c>
-    </row>
-    <row r="112" spans="1:18">
+      <c r="T111">
+        <f>T110/12</f>
+        <v>38373.208333333336</v>
+      </c>
+    </row>
+    <row r="112" spans="1:20">
       <c r="B112">
         <v>5500</v>
       </c>
-    </row>
-    <row r="113" spans="2:2">
+      <c r="T112">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="113" spans="2:20">
       <c r="B113">
         <v>5142</v>
       </c>
-    </row>
-    <row r="114" spans="2:2">
+      <c r="J113">
+        <f>30854/4</f>
+        <v>7713.5</v>
+      </c>
+      <c r="K113">
+        <f>J113*2.5</f>
+        <v>19283.75</v>
+      </c>
+      <c r="T113">
+        <v>12000</v>
+      </c>
+    </row>
+    <row r="114" spans="2:20">
       <c r="B114">
         <v>16000</v>
       </c>
-    </row>
-    <row r="115" spans="2:2">
+      <c r="T114">
+        <v>16000</v>
+      </c>
+    </row>
+    <row r="115" spans="2:20">
       <c r="B115">
         <v>1928</v>
       </c>
+      <c r="T115">
+        <f>SUM(T111:T114)</f>
+        <v>72373.208333333343</v>
+      </c>
+    </row>
+    <row r="116" spans="2:20">
+      <c r="T116">
+        <f>T115*12</f>
+        <v>868478.50000000012</v>
+      </c>
+    </row>
+    <row r="117" spans="2:20">
+      <c r="B117">
+        <f>SUM(B97:D108)</f>
+        <v>460478.5</v>
+      </c>
+      <c r="C117">
+        <v>216000</v>
+      </c>
+    </row>
+    <row r="118" spans="2:20">
+      <c r="B118">
+        <f>B117/12</f>
+        <v>38373.208333333336</v>
+      </c>
+    </row>
+    <row r="121" spans="2:20">
+      <c r="B121">
+        <v>77135</v>
+      </c>
+    </row>
+    <row r="122" spans="2:20">
+      <c r="B122">
+        <v>77135</v>
+      </c>
+    </row>
+    <row r="123" spans="2:20">
+      <c r="B123">
+        <v>77135</v>
+      </c>
+    </row>
+    <row r="124" spans="2:20">
+      <c r="B124">
+        <v>77135</v>
+      </c>
+    </row>
+    <row r="125" spans="2:20">
+      <c r="B125">
+        <v>77135</v>
+      </c>
+    </row>
+    <row r="126" spans="2:20">
+      <c r="B126">
+        <v>77135</v>
+      </c>
+    </row>
+    <row r="127" spans="2:20">
+      <c r="B127">
+        <v>77135</v>
+      </c>
+    </row>
+    <row r="128" spans="2:20">
+      <c r="B128">
+        <v>77135</v>
+      </c>
+    </row>
+    <row r="129" spans="2:2">
+      <c r="B129">
+        <v>77135</v>
+      </c>
+    </row>
+    <row r="130" spans="2:2">
+      <c r="B130">
+        <v>77135</v>
+      </c>
+    </row>
+    <row r="131" spans="2:2">
+      <c r="B131">
+        <v>77135</v>
+      </c>
+    </row>
+    <row r="132" spans="2:2">
+      <c r="B132">
+        <v>77135</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="B88" r:id="rId1" tooltip="View Details" display="https://ebanking.indiapost.gov.in/corp/Finacle;jsessionid=0000RapsQKDoL_lCqroYlzxTXT4:185s9fpmp?bwayparam=YaoD7lr%2Fdl6kDkAkrurLes2Jx92yIrK92YFFa3frMTVbhQdHnE6fstALqk3egHpdr585TWVSI4ER0X%2Be4QGsudjK5zY4RIlkrLDjSTKl3FNTO9Q13uzArVxxc4izbs0k%0D%0ApnvGISqy6AzyJ58%2Bdk%2F5cAJc5PZmU0qWy4CIHVXrNCI%3D" xr:uid="{6A0E39F9-6C31-4049-A88E-713FCCF1B244}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
+  <pageSetup orientation="portrait" r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -7529,10 +7727,10 @@
       </c>
       <c r="C1" s="28"/>
       <c r="D1" s="29" t="s">
+        <v>206</v>
+      </c>
+      <c r="E1" s="30" t="s">
         <v>207</v>
-      </c>
-      <c r="E1" s="30" t="s">
-        <v>208</v>
       </c>
       <c r="F1" s="31">
         <v>786</v>
@@ -7551,10 +7749,10 @@
       </c>
       <c r="C2" s="28"/>
       <c r="D2" s="29" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E2" s="30" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="F2" s="31">
         <v>786</v>
@@ -7572,13 +7770,13 @@
         <v>45753</v>
       </c>
       <c r="C3" s="34" t="s">
+        <v>209</v>
+      </c>
+      <c r="D3" s="34" t="s">
         <v>210</v>
       </c>
-      <c r="D3" s="34" t="s">
+      <c r="E3" s="34" t="s">
         <v>211</v>
-      </c>
-      <c r="E3" s="34" t="s">
-        <v>212</v>
       </c>
       <c r="F3" s="34"/>
       <c r="G3" s="35"/>
@@ -7657,10 +7855,10 @@
       </c>
       <c r="C9" s="28"/>
       <c r="D9" s="29" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="E9" s="30" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="F9" s="31">
         <v>786</v>
@@ -7679,10 +7877,10 @@
       </c>
       <c r="C10" s="28"/>
       <c r="D10" s="29" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="E10" s="30" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="F10" s="31">
         <v>786</v>
@@ -7741,10 +7939,10 @@
       </c>
       <c r="C13" s="28"/>
       <c r="D13" s="29" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E13" s="30" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="F13" s="31">
         <v>786</v>
@@ -7763,10 +7961,10 @@
       </c>
       <c r="C14" s="28"/>
       <c r="D14" s="29" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="E14" s="30" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="F14" s="31">
         <v>786</v>
@@ -7784,10 +7982,10 @@
         <v>45835</v>
       </c>
       <c r="C15" s="45"/>
-      <c r="D15" s="72" t="s">
-        <v>217</v>
-      </c>
-      <c r="E15" s="73"/>
+      <c r="D15" s="73" t="s">
+        <v>216</v>
+      </c>
+      <c r="E15" s="74"/>
       <c r="F15" s="31">
         <v>786</v>
       </c>
@@ -7832,7 +8030,7 @@
         <v>0</v>
       </c>
       <c r="D18" s="46" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E18" s="47"/>
       <c r="F18" s="31">
@@ -7854,7 +8052,7 @@
         <v>0</v>
       </c>
       <c r="D19" s="46" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="E19" s="47"/>
       <c r="F19" s="31">
@@ -7874,7 +8072,7 @@
       </c>
       <c r="C20" s="28"/>
       <c r="D20" s="29" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E20" s="30"/>
       <c r="F20" s="31">
@@ -7894,7 +8092,7 @@
       </c>
       <c r="C21" s="28"/>
       <c r="D21" s="29" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="E21" s="30"/>
       <c r="F21" s="31">
@@ -7914,7 +8112,7 @@
       </c>
       <c r="C22" s="28"/>
       <c r="D22" s="29" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="E22" s="30"/>
       <c r="F22" s="31">
@@ -8022,7 +8220,7 @@
       </c>
       <c r="C29" s="28"/>
       <c r="D29" s="29" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E29" s="30"/>
       <c r="F29" s="31">
@@ -8042,7 +8240,7 @@
       </c>
       <c r="C30" s="28"/>
       <c r="D30" s="29" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E30" s="30"/>
       <c r="F30" s="31">
@@ -8062,7 +8260,7 @@
       </c>
       <c r="C31" s="28"/>
       <c r="D31" s="29" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="E31" s="30"/>
       <c r="F31" s="31">
@@ -8096,10 +8294,10 @@
       </c>
       <c r="C33" s="28"/>
       <c r="D33" s="29" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E33" s="30" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="F33" s="31">
         <v>786</v>
@@ -8118,10 +8316,10 @@
       </c>
       <c r="C34" s="28"/>
       <c r="D34" s="29" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="E34" s="30" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="F34" s="31">
         <v>786</v>
